--- a/informes_data/ACB/2025-26/Regular_Season/aggregate_individual/AGG_IND_MoraBanc Andorra.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/aggregate_individual/AGG_IND_MoraBanc Andorra.xlsx
@@ -562,76 +562,76 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D2" t="n">
-        <v>32.8494</v>
+        <v>44.2871</v>
       </c>
       <c r="E2" t="n">
-        <v>41.8454</v>
+        <v>53.7839</v>
       </c>
       <c r="F2" t="n">
-        <v>-8.9964</v>
+        <v>-9.496</v>
       </c>
       <c r="G2" t="n">
-        <v>8.8376</v>
+        <v>22.604</v>
       </c>
       <c r="H2" t="n">
-        <v>15.4004</v>
+        <v>26.3773</v>
       </c>
       <c r="I2" t="n">
-        <v>-6.562900000000001</v>
+        <v>-3.7734</v>
       </c>
       <c r="J2" t="n">
-        <v>35.4068</v>
+        <v>51.5518</v>
       </c>
       <c r="K2" t="n">
-        <v>28.0259</v>
+        <v>40.7764</v>
       </c>
       <c r="L2" t="n">
-        <v>7.3808</v>
+        <v>10.7753</v>
       </c>
       <c r="M2" t="n">
-        <v>-26.5692</v>
+        <v>-28.9482</v>
       </c>
       <c r="N2" t="n">
-        <v>-12.6257</v>
+        <v>-14.3989</v>
       </c>
       <c r="O2" t="n">
-        <v>-13.9435</v>
+        <v>-14.549</v>
       </c>
       <c r="P2" t="n">
-        <v>-23.137</v>
+        <v>-33.0064</v>
       </c>
       <c r="Q2" t="n">
-        <v>-57.389</v>
+        <v>-73.9804</v>
       </c>
       <c r="R2" t="n">
-        <v>34.2516</v>
+        <v>40.9737</v>
       </c>
       <c r="S2" t="n">
-        <v>14.0481</v>
+        <v>21.5624</v>
       </c>
       <c r="T2" t="n">
-        <v>15.428</v>
+        <v>23.0837</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.3801</v>
+        <v>-1.5215</v>
       </c>
       <c r="V2" t="n">
-        <v>33.1009</v>
+        <v>33.1278</v>
       </c>
       <c r="W2" t="n">
-        <v>48.3994</v>
+        <v>53.1284</v>
       </c>
       <c r="X2" t="n">
-        <v>-15.2985</v>
+        <v>-20.0007</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R. GUERRERO</t>
+          <t>R. LUZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D3" t="n">
-        <v>10.8585</v>
+        <v>23.3906</v>
       </c>
       <c r="E3" t="n">
-        <v>17.9125</v>
+        <v>26.0946</v>
       </c>
       <c r="F3" t="n">
-        <v>-7.0544</v>
+        <v>-2.7038</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.6915999999999998</v>
+        <v>46.5862</v>
       </c>
       <c r="H3" t="n">
-        <v>-2.7821</v>
+        <v>13.7842</v>
       </c>
       <c r="I3" t="n">
-        <v>2.0907</v>
+        <v>32.8021</v>
       </c>
       <c r="J3" t="n">
-        <v>11.6939</v>
+        <v>63.5969</v>
       </c>
       <c r="K3" t="n">
-        <v>7.066599999999999</v>
+        <v>23.9801</v>
       </c>
       <c r="L3" t="n">
-        <v>4.6273</v>
+        <v>39.6166</v>
       </c>
       <c r="M3" t="n">
-        <v>-12.3855</v>
+        <v>-17.0107</v>
       </c>
       <c r="N3" t="n">
-        <v>-9.848800000000001</v>
+        <v>-10.1959</v>
       </c>
       <c r="O3" t="n">
-        <v>-2.5366</v>
+        <v>-6.8148</v>
       </c>
       <c r="P3" t="n">
-        <v>6.5781</v>
+        <v>-22.3077</v>
       </c>
       <c r="Q3" t="n">
-        <v>-9.526899999999999</v>
+        <v>-51.2173</v>
       </c>
       <c r="R3" t="n">
-        <v>16.1052</v>
+        <v>28.9091</v>
       </c>
       <c r="S3" t="n">
-        <v>14.0796</v>
+        <v>3.2786</v>
       </c>
       <c r="T3" t="n">
-        <v>10.25</v>
+        <v>1.0846</v>
       </c>
       <c r="U3" t="n">
-        <v>3.8296</v>
+        <v>2.1942</v>
       </c>
       <c r="V3" t="n">
-        <v>-9.108000000000001</v>
+        <v>-4.1663</v>
       </c>
       <c r="W3" t="n">
-        <v>5.495699999999999</v>
+        <v>12.6303</v>
       </c>
       <c r="X3" t="n">
-        <v>-14.6037</v>
+        <v>-16.7965</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R. LUZ</t>
+          <t>R. GUERRERO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,70 +718,70 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="D4" t="n">
-        <v>9.480599999999999</v>
+        <v>14.0165</v>
       </c>
       <c r="E4" t="n">
-        <v>15.8804</v>
+        <v>20.1811</v>
       </c>
       <c r="F4" t="n">
-        <v>-6.3997</v>
+        <v>-6.164900000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>31.8529</v>
+        <v>1.003</v>
       </c>
       <c r="H4" t="n">
-        <v>7.270499999999999</v>
+        <v>-3.591899999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>24.5823</v>
+        <v>4.5952</v>
       </c>
       <c r="J4" t="n">
-        <v>46.75</v>
+        <v>12.6921</v>
       </c>
       <c r="K4" t="n">
-        <v>17.2835</v>
+        <v>7.144</v>
       </c>
       <c r="L4" t="n">
-        <v>29.4668</v>
+        <v>5.548</v>
       </c>
       <c r="M4" t="n">
-        <v>-14.8972</v>
+        <v>-11.6894</v>
       </c>
       <c r="N4" t="n">
-        <v>-10.0129</v>
+        <v>-10.7356</v>
       </c>
       <c r="O4" t="n">
-        <v>-4.8845</v>
+        <v>-0.9539000000000002</v>
       </c>
       <c r="P4" t="n">
-        <v>-23.1369</v>
+        <v>7.284199999999999</v>
       </c>
       <c r="Q4" t="n">
-        <v>-44.0056</v>
+        <v>-10.9263</v>
       </c>
       <c r="R4" t="n">
-        <v>20.8684</v>
+        <v>18.2107</v>
       </c>
       <c r="S4" t="n">
-        <v>1.7418</v>
+        <v>16.2031</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7624000000000002</v>
+        <v>11.8638</v>
       </c>
       <c r="U4" t="n">
-        <v>0.9795</v>
+        <v>4.3393</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.9772000000000005</v>
+        <v>-10.4741</v>
       </c>
       <c r="W4" t="n">
-        <v>12.3732</v>
+        <v>6.5518</v>
       </c>
       <c r="X4" t="n">
-        <v>-13.3503</v>
+        <v>-17.0256</v>
       </c>
     </row>
     <row r="5">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D5" t="n">
-        <v>0.184099999999999</v>
+        <v>10.1043</v>
       </c>
       <c r="E5" t="n">
-        <v>13.2378</v>
+        <v>27.1635</v>
       </c>
       <c r="F5" t="n">
-        <v>-13.0537</v>
+        <v>-17.0593</v>
       </c>
       <c r="G5" t="n">
-        <v>-9.779299999999999</v>
+        <v>-1.7356</v>
       </c>
       <c r="H5" t="n">
-        <v>-36.1137</v>
+        <v>-38.0939</v>
       </c>
       <c r="I5" t="n">
-        <v>26.3347</v>
+        <v>36.3586</v>
       </c>
       <c r="J5" t="n">
-        <v>21.7487</v>
+        <v>35.2648</v>
       </c>
       <c r="K5" t="n">
-        <v>-11.9672</v>
+        <v>-10.8705</v>
       </c>
       <c r="L5" t="n">
-        <v>33.7159</v>
+        <v>46.1351</v>
       </c>
       <c r="M5" t="n">
-        <v>-31.5277</v>
+        <v>-37</v>
       </c>
       <c r="N5" t="n">
-        <v>-24.1466</v>
+        <v>-27.2239</v>
       </c>
       <c r="O5" t="n">
-        <v>-7.381</v>
+        <v>-9.7766</v>
       </c>
       <c r="P5" t="n">
-        <v>7.4857</v>
+        <v>8.1951</v>
       </c>
       <c r="Q5" t="n">
-        <v>-28.1274</v>
+        <v>-34.6003</v>
       </c>
       <c r="R5" t="n">
-        <v>35.6129</v>
+        <v>42.7951</v>
       </c>
       <c r="S5" t="n">
-        <v>-16.1165</v>
+        <v>-16.2888</v>
       </c>
       <c r="T5" t="n">
-        <v>-7.8936</v>
+        <v>-7.605399999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>-8.223100000000001</v>
+        <v>-8.683300000000001</v>
       </c>
       <c r="V5" t="n">
-        <v>18.5946</v>
+        <v>19.9337</v>
       </c>
       <c r="W5" t="n">
-        <v>27.51</v>
+        <v>34.1042</v>
       </c>
       <c r="X5" t="n">
-        <v>-8.9154</v>
+        <v>-14.1703</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. UDEZE</t>
+          <t>S. RICE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D6" t="n">
-        <v>-3.186799999999999</v>
+        <v>1.2806</v>
       </c>
       <c r="E6" t="n">
-        <v>12.6927</v>
+        <v>3.5813</v>
       </c>
       <c r="F6" t="n">
-        <v>-15.8795</v>
+        <v>-2.3006</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.9112999999999991</v>
+        <v>22.1923</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1379999999999999</v>
+        <v>6.1897</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.0491</v>
+        <v>16.0028</v>
       </c>
       <c r="J6" t="n">
-        <v>16.5682</v>
+        <v>33.1389</v>
       </c>
       <c r="K6" t="n">
-        <v>11.941</v>
+        <v>11.6443</v>
       </c>
       <c r="L6" t="n">
-        <v>4.6272</v>
+        <v>21.4943</v>
       </c>
       <c r="M6" t="n">
-        <v>-17.4796</v>
+        <v>-10.9463</v>
       </c>
       <c r="N6" t="n">
-        <v>-11.8032</v>
+        <v>-5.4544</v>
       </c>
       <c r="O6" t="n">
-        <v>-5.676699999999999</v>
+        <v>-5.4916</v>
       </c>
       <c r="P6" t="n">
-        <v>-5.6707</v>
+        <v>-19.804</v>
       </c>
       <c r="Q6" t="n">
-        <v>-24.2712</v>
+        <v>-45.9815</v>
       </c>
       <c r="R6" t="n">
-        <v>18.6006</v>
+        <v>26.1777</v>
       </c>
       <c r="S6" t="n">
-        <v>11.9436</v>
+        <v>-1.2545</v>
       </c>
       <c r="T6" t="n">
-        <v>9.5967</v>
+        <v>-0.7212</v>
       </c>
       <c r="U6" t="n">
-        <v>2.3466</v>
+        <v>-0.5328999999999999</v>
       </c>
       <c r="V6" t="n">
-        <v>-8.5482</v>
+        <v>0.1464999999999996</v>
       </c>
       <c r="W6" t="n">
-        <v>10.799</v>
+        <v>17.1458</v>
       </c>
       <c r="X6" t="n">
-        <v>-19.3469</v>
+        <v>-16.9991</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. GANAL</t>
+          <t>M. UDEZE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.4375</v>
+        <v>-3.076300000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.6785</v>
+        <v>12.3593</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2407</v>
+        <v>-15.4355</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.8511</v>
+        <v>-0.8314000000000004</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.5555</v>
+        <v>0.08600000000000074</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.2955</v>
+        <v>-0.9177000000000002</v>
       </c>
       <c r="J7" t="n">
-        <v>-2.142</v>
+        <v>16.3443</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.492</v>
+        <v>11.727</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.65</v>
+        <v>4.6173</v>
       </c>
       <c r="M7" t="n">
-        <v>0.291</v>
+        <v>-17.1757</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.06359999999999999</v>
+        <v>-11.6407</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3545</v>
+        <v>-5.534899999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.6806000000000001</v>
+        <v>-5.690700000000001</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1342</v>
+        <v>-24.3567</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4536</v>
+        <v>18.6661</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1349</v>
+        <v>11.9895</v>
       </c>
       <c r="T7" t="n">
-        <v>0.369</v>
+        <v>9.6614</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5038</v>
+        <v>2.3279</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.7712</v>
+        <v>-8.542899999999999</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.7712</v>
+        <v>10.7101</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-19.2531</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. RICE</t>
+          <t>A. GANAL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,70 +1030,70 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>-5.444799999999999</v>
+        <v>-3.4468</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.4634</v>
+        <v>-3.6988</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.9813</v>
+        <v>0.252</v>
       </c>
       <c r="G8" t="n">
-        <v>13.0629</v>
+        <v>-1.8551</v>
       </c>
       <c r="H8" t="n">
-        <v>3.7761</v>
+        <v>-0.5544</v>
       </c>
       <c r="I8" t="n">
-        <v>9.2867</v>
+        <v>-1.3007</v>
       </c>
       <c r="J8" t="n">
-        <v>20.0893</v>
+        <v>-2.158</v>
       </c>
       <c r="K8" t="n">
-        <v>6.8907</v>
+        <v>-0.4966</v>
       </c>
       <c r="L8" t="n">
-        <v>13.1988</v>
+        <v>-1.6614</v>
       </c>
       <c r="M8" t="n">
-        <v>-7.026599999999999</v>
+        <v>0.303</v>
       </c>
       <c r="N8" t="n">
-        <v>-3.1146</v>
+        <v>-0.0577</v>
       </c>
       <c r="O8" t="n">
-        <v>-3.9122</v>
+        <v>0.3608</v>
       </c>
       <c r="P8" t="n">
-        <v>-11.3417</v>
+        <v>-0.6830000000000001</v>
       </c>
       <c r="Q8" t="n">
-        <v>-29.2615</v>
+        <v>-1.1382</v>
       </c>
       <c r="R8" t="n">
-        <v>17.9199</v>
+        <v>0.4552</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.2527</v>
+        <v>-0.1348</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.9083</v>
+        <v>0.3714</v>
       </c>
       <c r="U8" t="n">
-        <v>0.6555000000000001</v>
+        <v>-0.5062</v>
       </c>
       <c r="V8" t="n">
-        <v>-5.9131</v>
+        <v>-0.7739</v>
       </c>
       <c r="W8" t="n">
-        <v>7.617</v>
+        <v>-0.7739</v>
       </c>
       <c r="X8" t="n">
-        <v>-13.53</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,67 +1111,67 @@
         <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>-7.267500000000001</v>
+        <v>-7.2754</v>
       </c>
       <c r="E9" t="n">
-        <v>-6.7315</v>
+        <v>-6.8094</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5359999999999999</v>
+        <v>-0.466</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.0275</v>
+        <v>-1.0133</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.3926</v>
+        <v>-1.3766</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3651</v>
+        <v>0.3633</v>
       </c>
       <c r="J9" t="n">
-        <v>1.0647</v>
+        <v>1.0168</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.003999999999999969</v>
+        <v>-0.02469999999999992</v>
       </c>
       <c r="L9" t="n">
-        <v>1.0688</v>
+        <v>1.0415</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.0922</v>
+        <v>-2.03</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.3889</v>
+        <v>-1.3519</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.7034999999999999</v>
+        <v>-0.6781</v>
       </c>
       <c r="P9" t="n">
-        <v>-5.897600000000001</v>
+        <v>-5.9183</v>
       </c>
       <c r="Q9" t="n">
-        <v>-9.3002</v>
+        <v>-9.3329</v>
       </c>
       <c r="R9" t="n">
-        <v>3.4025</v>
+        <v>3.4145</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3424</v>
+        <v>-0.3437</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4113</v>
+        <v>0.4172</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.7537</v>
+        <v>-0.7609</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="10">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D10" t="n">
-        <v>-8.370000000000001</v>
+        <v>-10.5201</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.408099999999999</v>
+        <v>-5.414899999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.9621</v>
+        <v>-5.104799999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>-14.5812</v>
+        <v>-12.5678</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.09370000000000034</v>
+        <v>1.9874</v>
       </c>
       <c r="I10" t="n">
-        <v>-14.4875</v>
+        <v>-14.5551</v>
       </c>
       <c r="J10" t="n">
-        <v>10.3831</v>
+        <v>13.632</v>
       </c>
       <c r="K10" t="n">
-        <v>15.9728</v>
+        <v>19.8</v>
       </c>
       <c r="L10" t="n">
-        <v>-5.589600000000001</v>
+        <v>-6.1685</v>
       </c>
       <c r="M10" t="n">
-        <v>-24.9641</v>
+        <v>-26.1998</v>
       </c>
       <c r="N10" t="n">
-        <v>-16.0663</v>
+        <v>-17.8127</v>
       </c>
       <c r="O10" t="n">
-        <v>-8.8978</v>
+        <v>-8.387</v>
       </c>
       <c r="P10" t="n">
-        <v>12.0222</v>
+        <v>12.7473</v>
       </c>
       <c r="Q10" t="n">
-        <v>-24.9518</v>
+        <v>-29.82</v>
       </c>
       <c r="R10" t="n">
-        <v>36.9739</v>
+        <v>42.5674</v>
       </c>
       <c r="S10" t="n">
-        <v>-5.5538</v>
+        <v>-7.187</v>
       </c>
       <c r="T10" t="n">
-        <v>-4.0768</v>
+        <v>-5.7419</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.477</v>
+        <v>-1.445</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.2571999999999994</v>
+        <v>-3.5124</v>
       </c>
       <c r="W10" t="n">
-        <v>14.237</v>
+        <v>16.5146</v>
       </c>
       <c r="X10" t="n">
-        <v>-14.4944</v>
+        <v>-20.0275</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. BEST</t>
+          <t>X. CASTANEDA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="D11" t="n">
-        <v>-16.9225</v>
+        <v>-20.0646</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.9602999999999997</v>
+        <v>-12.5966</v>
       </c>
       <c r="F11" t="n">
-        <v>-15.9623</v>
+        <v>-7.4678</v>
       </c>
       <c r="G11" t="n">
-        <v>-17.667</v>
+        <v>-14.022</v>
       </c>
       <c r="H11" t="n">
-        <v>-22.7206</v>
+        <v>-19.1958</v>
       </c>
       <c r="I11" t="n">
-        <v>5.053900000000001</v>
+        <v>5.1739</v>
       </c>
       <c r="J11" t="n">
-        <v>13.2735</v>
+        <v>-0.8908</v>
       </c>
       <c r="K11" t="n">
-        <v>-6.6614</v>
+        <v>-9.1814</v>
       </c>
       <c r="L11" t="n">
-        <v>19.9352</v>
+        <v>8.290699999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>-30.9405</v>
+        <v>-13.1312</v>
       </c>
       <c r="N11" t="n">
-        <v>-16.0592</v>
+        <v>-10.0147</v>
       </c>
       <c r="O11" t="n">
-        <v>-14.8816</v>
+        <v>-3.1167</v>
       </c>
       <c r="P11" t="n">
-        <v>14.0637</v>
+        <v>-7.284199999999999</v>
       </c>
       <c r="Q11" t="n">
-        <v>-31.3032</v>
+        <v>-17.5277</v>
       </c>
       <c r="R11" t="n">
-        <v>45.3667</v>
+        <v>10.2436</v>
       </c>
       <c r="S11" t="n">
-        <v>-20.0678</v>
+        <v>-4.5925</v>
       </c>
       <c r="T11" t="n">
-        <v>-9.348100000000001</v>
+        <v>-5.4747</v>
       </c>
       <c r="U11" t="n">
-        <v>-10.7201</v>
+        <v>0.8822</v>
       </c>
       <c r="V11" t="n">
-        <v>6.7485</v>
+        <v>5.8344</v>
       </c>
       <c r="W11" t="n">
-        <v>26.4173</v>
+        <v>11.2965</v>
       </c>
       <c r="X11" t="n">
-        <v>-19.6688</v>
+        <v>-5.462499999999999</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X. CASTANEDA</t>
+          <t>C. ORTEGA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="D12" t="n">
-        <v>-19.9017</v>
+        <v>-22.1566</v>
       </c>
       <c r="E12" t="n">
-        <v>-12.2158</v>
+        <v>-16.8958</v>
       </c>
       <c r="F12" t="n">
-        <v>-7.6859</v>
+        <v>-5.2607</v>
       </c>
       <c r="G12" t="n">
-        <v>-13.9128</v>
+        <v>-24.3234</v>
       </c>
       <c r="H12" t="n">
-        <v>-19.1765</v>
+        <v>-19.8714</v>
       </c>
       <c r="I12" t="n">
-        <v>5.2638</v>
+        <v>-4.4522</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.6263999999999994</v>
+        <v>-8.135</v>
       </c>
       <c r="K12" t="n">
-        <v>-9.064299999999999</v>
+        <v>-5.3959</v>
       </c>
       <c r="L12" t="n">
-        <v>8.437799999999999</v>
+        <v>-2.7392</v>
       </c>
       <c r="M12" t="n">
-        <v>-13.2867</v>
+        <v>-16.1886</v>
       </c>
       <c r="N12" t="n">
-        <v>-10.1123</v>
+        <v>-14.4755</v>
       </c>
       <c r="O12" t="n">
-        <v>-3.1743</v>
+        <v>-1.713</v>
       </c>
       <c r="P12" t="n">
-        <v>-7.258599999999999</v>
+        <v>11.1541</v>
       </c>
       <c r="Q12" t="n">
-        <v>-17.4662</v>
+        <v>-14.1133</v>
       </c>
       <c r="R12" t="n">
-        <v>10.2076</v>
+        <v>25.2673</v>
       </c>
       <c r="S12" t="n">
-        <v>-4.5793</v>
+        <v>-2.7279</v>
       </c>
       <c r="T12" t="n">
-        <v>-5.4679</v>
+        <v>-2.905</v>
       </c>
       <c r="U12" t="n">
-        <v>0.8888</v>
+        <v>0.177</v>
       </c>
       <c r="V12" t="n">
-        <v>5.849</v>
+        <v>-6.258600000000001</v>
       </c>
       <c r="W12" t="n">
-        <v>11.3447</v>
+        <v>8.2577</v>
       </c>
       <c r="X12" t="n">
-        <v>-5.4957</v>
+        <v>-14.5163</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Y. PONS</t>
+          <t>K. KOSTADINOV</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D13" t="n">
-        <v>-19.9138</v>
+        <v>-22.6408</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.0961</v>
+        <v>3.437100000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>-12.8176</v>
+        <v>-26.0779</v>
       </c>
       <c r="G13" t="n">
-        <v>-5.3703</v>
+        <v>-7.879099999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.5125</v>
+        <v>-6.1991</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.857699999999999</v>
+        <v>-1.6804</v>
       </c>
       <c r="J13" t="n">
-        <v>17.4962</v>
+        <v>12.963</v>
       </c>
       <c r="K13" t="n">
-        <v>11.1046</v>
+        <v>8.7342</v>
       </c>
       <c r="L13" t="n">
-        <v>6.391999999999999</v>
+        <v>4.2287</v>
       </c>
       <c r="M13" t="n">
-        <v>-22.8666</v>
+        <v>-20.842</v>
       </c>
       <c r="N13" t="n">
-        <v>-13.6169</v>
+        <v>-14.9331</v>
       </c>
       <c r="O13" t="n">
-        <v>-9.249600000000001</v>
+        <v>-5.9091</v>
       </c>
       <c r="P13" t="n">
-        <v>16.1052</v>
+        <v>-4.5527</v>
       </c>
       <c r="Q13" t="n">
-        <v>-22.4566</v>
+        <v>-27.9988</v>
       </c>
       <c r="R13" t="n">
-        <v>38.5619</v>
+        <v>23.4464</v>
       </c>
       <c r="S13" t="n">
-        <v>-13.7443</v>
+        <v>8.5185</v>
       </c>
       <c r="T13" t="n">
-        <v>-8.0174</v>
+        <v>12.3085</v>
       </c>
       <c r="U13" t="n">
-        <v>-5.727</v>
+        <v>-3.7892</v>
       </c>
       <c r="V13" t="n">
-        <v>-16.9047</v>
+        <v>-18.7276</v>
       </c>
       <c r="W13" t="n">
-        <v>5.8815</v>
+        <v>6.1646</v>
       </c>
       <c r="X13" t="n">
-        <v>-22.7861</v>
+        <v>-24.8923</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C. ORTEGA</t>
+          <t>A. BEST</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D14" t="n">
-        <v>-21.4262</v>
+        <v>-27.5442</v>
       </c>
       <c r="E14" t="n">
-        <v>-15.0111</v>
+        <v>-9.019899999999998</v>
       </c>
       <c r="F14" t="n">
-        <v>-6.415299999999999</v>
+        <v>-18.5241</v>
       </c>
       <c r="G14" t="n">
-        <v>-23.1945</v>
+        <v>-28.7917</v>
       </c>
       <c r="H14" t="n">
-        <v>-20.8094</v>
+        <v>-23.8937</v>
       </c>
       <c r="I14" t="n">
-        <v>-2.384799999999999</v>
+        <v>-4.8984</v>
       </c>
       <c r="J14" t="n">
-        <v>-6.401599999999999</v>
+        <v>5.4857</v>
       </c>
       <c r="K14" t="n">
-        <v>-6.227499999999999</v>
+        <v>-6.434500000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.1742000000000001</v>
+        <v>11.92</v>
       </c>
       <c r="M14" t="n">
-        <v>-16.7927</v>
+        <v>-34.2771</v>
       </c>
       <c r="N14" t="n">
-        <v>-14.5823</v>
+        <v>-17.4589</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.2108</v>
+        <v>-16.8182</v>
       </c>
       <c r="P14" t="n">
-        <v>10.6612</v>
+        <v>11.837</v>
       </c>
       <c r="Q14" t="n">
-        <v>-12.9295</v>
+        <v>-40.7462</v>
       </c>
       <c r="R14" t="n">
-        <v>23.5906</v>
+        <v>52.5829</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.6131</v>
+        <v>-21.9275</v>
       </c>
       <c r="T14" t="n">
-        <v>-2.879</v>
+        <v>-7.3188</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2660999999999999</v>
+        <v>-14.6085</v>
       </c>
       <c r="V14" t="n">
-        <v>-6.2795</v>
+        <v>11.3382</v>
       </c>
       <c r="W14" t="n">
-        <v>7.1991</v>
+        <v>33.5595</v>
       </c>
       <c r="X14" t="n">
-        <v>-13.4786</v>
+        <v>-22.2211</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. MCKOY</t>
+          <t>Y. PONS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D15" t="n">
-        <v>-26.7643</v>
+        <v>-29.0368</v>
       </c>
       <c r="E15" t="n">
-        <v>-11.8901</v>
+        <v>-9.1594</v>
       </c>
       <c r="F15" t="n">
-        <v>-14.8745</v>
+        <v>-19.8773</v>
       </c>
       <c r="G15" t="n">
-        <v>-44.6334</v>
+        <v>-5.2949</v>
       </c>
       <c r="H15" t="n">
-        <v>-25.9927</v>
+        <v>-3.676399999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>-18.6402</v>
+        <v>-1.6185</v>
       </c>
       <c r="J15" t="n">
-        <v>-13.3649</v>
+        <v>20.0337</v>
       </c>
       <c r="K15" t="n">
-        <v>-8.7936</v>
+        <v>11.2107</v>
       </c>
       <c r="L15" t="n">
-        <v>-4.5712</v>
+        <v>8.822700000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>-31.268</v>
+        <v>-25.3285</v>
       </c>
       <c r="N15" t="n">
-        <v>-17.1988</v>
+        <v>-14.8872</v>
       </c>
       <c r="O15" t="n">
-        <v>-14.0696</v>
+        <v>-10.4419</v>
       </c>
       <c r="P15" t="n">
-        <v>9.7536</v>
+        <v>20.487</v>
       </c>
       <c r="Q15" t="n">
-        <v>-21.5493</v>
+        <v>-25.2674</v>
       </c>
       <c r="R15" t="n">
-        <v>31.3028</v>
+        <v>45.7543</v>
       </c>
       <c r="S15" t="n">
-        <v>4.3228</v>
+        <v>-16.3457</v>
       </c>
       <c r="T15" t="n">
-        <v>3.644600000000001</v>
+        <v>-9.933</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6778000000000002</v>
+        <v>-6.413</v>
       </c>
       <c r="V15" t="n">
-        <v>3.7921</v>
+        <v>-27.8829</v>
       </c>
       <c r="W15" t="n">
-        <v>19.3791</v>
+        <v>6.0073</v>
       </c>
       <c r="X15" t="n">
-        <v>-15.587</v>
+        <v>-33.89</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>K. KOSTADINOV</t>
+          <t>J. MCKOY</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,70 +1654,70 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="D16" t="n">
-        <v>-31.7865</v>
+        <v>-34.8152</v>
       </c>
       <c r="E16" t="n">
-        <v>-9.8889</v>
+        <v>-19.8745</v>
       </c>
       <c r="F16" t="n">
-        <v>-21.8973</v>
+        <v>-14.9407</v>
       </c>
       <c r="G16" t="n">
-        <v>-9.609900000000001</v>
+        <v>-53.0745</v>
       </c>
       <c r="H16" t="n">
-        <v>-10.4878</v>
+        <v>-30.863</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8776000000000002</v>
+        <v>-22.2115</v>
       </c>
       <c r="J16" t="n">
-        <v>5.704599999999999</v>
+        <v>-17.4446</v>
       </c>
       <c r="K16" t="n">
-        <v>2.9995</v>
+        <v>-10.8958</v>
       </c>
       <c r="L16" t="n">
-        <v>2.7052</v>
+        <v>-6.548499999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>-15.3146</v>
+        <v>-35.6302</v>
       </c>
       <c r="N16" t="n">
-        <v>-13.4872</v>
+        <v>-19.9668</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.8277</v>
+        <v>-15.6633</v>
       </c>
       <c r="P16" t="n">
-        <v>-7.2587</v>
+        <v>10.0156</v>
       </c>
       <c r="Q16" t="n">
-        <v>-24.2712</v>
+        <v>-28.6818</v>
       </c>
       <c r="R16" t="n">
-        <v>17.0126</v>
+        <v>38.6974</v>
       </c>
       <c r="S16" t="n">
-        <v>2.9957</v>
+        <v>6.8795</v>
       </c>
       <c r="T16" t="n">
-        <v>6.620800000000001</v>
+        <v>5.6941</v>
       </c>
       <c r="U16" t="n">
-        <v>-3.6251</v>
+        <v>1.1856</v>
       </c>
       <c r="V16" t="n">
-        <v>-17.9135</v>
+        <v>1.3639</v>
       </c>
       <c r="W16" t="n">
-        <v>2.0571</v>
+        <v>20.5573</v>
       </c>
       <c r="X16" t="n">
-        <v>-19.9705</v>
+        <v>-19.193</v>
       </c>
     </row>
     <row r="17">
@@ -1732,70 +1732,70 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D17" t="n">
-        <v>-66.8098</v>
+        <v>-72.46470000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>-38.9886</v>
+        <v>-42.9263</v>
       </c>
       <c r="F17" t="n">
-        <v>-27.8208</v>
+        <v>-29.5382</v>
       </c>
       <c r="G17" t="n">
-        <v>-16.5819</v>
+        <v>-4.2683</v>
       </c>
       <c r="H17" t="n">
-        <v>-20.3016</v>
+        <v>-14.3531</v>
       </c>
       <c r="I17" t="n">
-        <v>3.7199</v>
+        <v>10.085</v>
       </c>
       <c r="J17" t="n">
-        <v>26.339</v>
+        <v>44.0665</v>
       </c>
       <c r="K17" t="n">
-        <v>3.206699999999999</v>
+        <v>11.9134</v>
       </c>
       <c r="L17" t="n">
-        <v>23.132</v>
+        <v>32.1525</v>
       </c>
       <c r="M17" t="n">
-        <v>-42.9209</v>
+        <v>-48.3348</v>
       </c>
       <c r="N17" t="n">
-        <v>-23.5083</v>
+        <v>-26.2671</v>
       </c>
       <c r="O17" t="n">
-        <v>-19.4127</v>
+        <v>-22.0676</v>
       </c>
       <c r="P17" t="n">
-        <v>-45.5935</v>
+        <v>-59.8671</v>
       </c>
       <c r="Q17" t="n">
-        <v>-94.58959999999999</v>
+        <v>-117.4582</v>
       </c>
       <c r="R17" t="n">
-        <v>48.9962</v>
+        <v>57.5909</v>
       </c>
       <c r="S17" t="n">
-        <v>-29.1553</v>
+        <v>-34.3936</v>
       </c>
       <c r="T17" t="n">
-        <v>-16.7277</v>
+        <v>-20.3264</v>
       </c>
       <c r="U17" t="n">
-        <v>-12.4274</v>
+        <v>-14.0671</v>
       </c>
       <c r="V17" t="n">
-        <v>24.5211</v>
+        <v>26.0645</v>
       </c>
       <c r="W17" t="n">
-        <v>45.9891</v>
+        <v>50.791</v>
       </c>
       <c r="X17" t="n">
-        <v>-21.4684</v>
+        <v>-24.727</v>
       </c>
     </row>
     <row r="18">
@@ -1810,70 +1810,70 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>-177.8588</v>
+        <v>-159.9624</v>
       </c>
       <c r="E18" t="n">
-        <v>-12.76360000000001</v>
+        <v>20.2052</v>
       </c>
       <c r="F18" t="n">
-        <v>-165.0961</v>
+        <v>-180.1656</v>
       </c>
       <c r="G18" t="n">
-        <v>-106.0584</v>
+        <v>-63.27160000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>-136.3537</v>
+        <v>-113.2447</v>
       </c>
       <c r="I18" t="n">
-        <v>30.297</v>
+        <v>49.973</v>
       </c>
       <c r="J18" t="n">
-        <v>203.9831</v>
+        <v>281.1581</v>
       </c>
       <c r="K18" t="n">
-        <v>61.2813</v>
+        <v>103.6307</v>
       </c>
       <c r="L18" t="n">
-        <v>142.7028</v>
+        <v>177.5251</v>
       </c>
       <c r="M18" t="n">
-        <v>-310.0411</v>
+        <v>-344.4295</v>
       </c>
       <c r="N18" t="n">
-        <v>-197.6356</v>
+        <v>-216.875</v>
       </c>
       <c r="O18" t="n">
-        <v>-112.4076</v>
+        <v>-127.5549</v>
       </c>
       <c r="P18" t="n">
-        <v>-53.3056</v>
+        <v>-77.3938</v>
       </c>
       <c r="Q18" t="n">
-        <v>-452.5334</v>
+        <v>-553.1469999999999</v>
       </c>
       <c r="R18" t="n">
-        <v>399.227</v>
+        <v>475.7523</v>
       </c>
       <c r="S18" t="n">
-        <v>-44.42849999999999</v>
+        <v>-36.7644</v>
       </c>
       <c r="T18" t="n">
-        <v>-9.235999999999995</v>
+        <v>4.458300000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>-35.1934</v>
+        <v>-41.2214</v>
       </c>
       <c r="V18" t="n">
-        <v>25.93360000000001</v>
+        <v>17.47030000000001</v>
       </c>
       <c r="W18" t="n">
-        <v>245.0207</v>
+        <v>287.7347</v>
       </c>
       <c r="X18" t="n">
-        <v>-219.087</v>
+        <v>-270.2645</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/aggregate_individual/AGG_IND_MoraBanc Andorra.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/aggregate_individual/AGG_IND_MoraBanc Andorra.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. PUSTOVYI</t>
+          <t>K. KURIC</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -562,70 +562,70 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D2" t="n">
-        <v>44.2871</v>
+        <v>25.403</v>
       </c>
       <c r="E2" t="n">
-        <v>53.7839</v>
+        <v>37.6845</v>
       </c>
       <c r="F2" t="n">
-        <v>-9.496</v>
+        <v>-12.2817</v>
       </c>
       <c r="G2" t="n">
-        <v>22.604</v>
+        <v>-1.7356</v>
       </c>
       <c r="H2" t="n">
-        <v>26.3773</v>
+        <v>-38.0939</v>
       </c>
       <c r="I2" t="n">
-        <v>-3.7734</v>
+        <v>36.3586</v>
       </c>
       <c r="J2" t="n">
-        <v>51.5518</v>
+        <v>35.2648</v>
       </c>
       <c r="K2" t="n">
-        <v>40.7764</v>
+        <v>-10.8705</v>
       </c>
       <c r="L2" t="n">
-        <v>10.7753</v>
+        <v>46.1351</v>
       </c>
       <c r="M2" t="n">
-        <v>-28.9482</v>
+        <v>-37</v>
       </c>
       <c r="N2" t="n">
-        <v>-14.3989</v>
+        <v>-27.2239</v>
       </c>
       <c r="O2" t="n">
-        <v>-14.549</v>
+        <v>-9.7766</v>
       </c>
       <c r="P2" t="n">
-        <v>-33.0064</v>
+        <v>8.1951</v>
       </c>
       <c r="Q2" t="n">
-        <v>-73.9804</v>
+        <v>-34.6003</v>
       </c>
       <c r="R2" t="n">
-        <v>40.9737</v>
+        <v>42.7951</v>
       </c>
       <c r="S2" t="n">
-        <v>21.5624</v>
+        <v>-0.9903</v>
       </c>
       <c r="T2" t="n">
-        <v>23.0837</v>
+        <v>2.9162</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.5215</v>
+        <v>-3.9061</v>
       </c>
       <c r="V2" t="n">
-        <v>33.1278</v>
+        <v>19.9337</v>
       </c>
       <c r="W2" t="n">
-        <v>53.1284</v>
+        <v>34.1042</v>
       </c>
       <c r="X2" t="n">
-        <v>-20.0007</v>
+        <v>-14.1703</v>
       </c>
     </row>
     <row r="3">
@@ -643,13 +643,13 @@
         <v>28</v>
       </c>
       <c r="D3" t="n">
-        <v>23.3906</v>
+        <v>24.8595</v>
       </c>
       <c r="E3" t="n">
-        <v>26.0946</v>
+        <v>26.8608</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.7038</v>
+        <v>-2.0016</v>
       </c>
       <c r="G3" t="n">
         <v>46.5862</v>
@@ -688,13 +688,13 @@
         <v>28.9091</v>
       </c>
       <c r="S3" t="n">
-        <v>3.2786</v>
+        <v>4.7477</v>
       </c>
       <c r="T3" t="n">
-        <v>1.0846</v>
+        <v>1.8515</v>
       </c>
       <c r="U3" t="n">
-        <v>2.1942</v>
+        <v>2.8966</v>
       </c>
       <c r="V3" t="n">
         <v>-4.1663</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R. GUERRERO</t>
+          <t>A. PUSTOVYI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D4" t="n">
-        <v>14.0165</v>
+        <v>24.1121</v>
       </c>
       <c r="E4" t="n">
-        <v>20.1811</v>
+        <v>35.0697</v>
       </c>
       <c r="F4" t="n">
-        <v>-6.164900000000001</v>
+        <v>-10.9573</v>
       </c>
       <c r="G4" t="n">
-        <v>1.003</v>
+        <v>22.604</v>
       </c>
       <c r="H4" t="n">
-        <v>-3.591899999999999</v>
+        <v>26.3773</v>
       </c>
       <c r="I4" t="n">
-        <v>4.5952</v>
+        <v>-3.7734</v>
       </c>
       <c r="J4" t="n">
-        <v>12.6921</v>
+        <v>51.5518</v>
       </c>
       <c r="K4" t="n">
-        <v>7.144</v>
+        <v>40.7764</v>
       </c>
       <c r="L4" t="n">
-        <v>5.548</v>
+        <v>10.7753</v>
       </c>
       <c r="M4" t="n">
-        <v>-11.6894</v>
+        <v>-28.9482</v>
       </c>
       <c r="N4" t="n">
-        <v>-10.7356</v>
+        <v>-14.3989</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.9539000000000002</v>
+        <v>-14.549</v>
       </c>
       <c r="P4" t="n">
-        <v>7.284199999999999</v>
+        <v>-33.0064</v>
       </c>
       <c r="Q4" t="n">
-        <v>-10.9263</v>
+        <v>-73.9804</v>
       </c>
       <c r="R4" t="n">
-        <v>18.2107</v>
+        <v>40.9737</v>
       </c>
       <c r="S4" t="n">
-        <v>16.2031</v>
+        <v>1.3874</v>
       </c>
       <c r="T4" t="n">
-        <v>11.8638</v>
+        <v>4.3699</v>
       </c>
       <c r="U4" t="n">
-        <v>4.3393</v>
+        <v>-2.982499999999999</v>
       </c>
       <c r="V4" t="n">
-        <v>-10.4741</v>
+        <v>33.1278</v>
       </c>
       <c r="W4" t="n">
-        <v>6.5518</v>
+        <v>53.1284</v>
       </c>
       <c r="X4" t="n">
-        <v>-17.0256</v>
+        <v>-20.0007</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>K. KURIC</t>
+          <t>R. GUERRERO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,70 +796,70 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D5" t="n">
-        <v>10.1043</v>
+        <v>6.086500000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>27.1635</v>
+        <v>13.7227</v>
       </c>
       <c r="F5" t="n">
-        <v>-17.0593</v>
+        <v>-7.636</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.7356</v>
+        <v>1.003</v>
       </c>
       <c r="H5" t="n">
-        <v>-38.0939</v>
+        <v>-3.591899999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>36.3586</v>
+        <v>4.5952</v>
       </c>
       <c r="J5" t="n">
-        <v>35.2648</v>
+        <v>12.6921</v>
       </c>
       <c r="K5" t="n">
-        <v>-10.8705</v>
+        <v>7.144</v>
       </c>
       <c r="L5" t="n">
-        <v>46.1351</v>
+        <v>5.548</v>
       </c>
       <c r="M5" t="n">
-        <v>-37</v>
+        <v>-11.6894</v>
       </c>
       <c r="N5" t="n">
-        <v>-27.2239</v>
+        <v>-10.7356</v>
       </c>
       <c r="O5" t="n">
-        <v>-9.7766</v>
+        <v>-0.9539000000000002</v>
       </c>
       <c r="P5" t="n">
-        <v>8.1951</v>
+        <v>7.284199999999999</v>
       </c>
       <c r="Q5" t="n">
-        <v>-34.6003</v>
+        <v>-10.9263</v>
       </c>
       <c r="R5" t="n">
-        <v>42.7951</v>
+        <v>18.2107</v>
       </c>
       <c r="S5" t="n">
-        <v>-16.2888</v>
+        <v>8.2737</v>
       </c>
       <c r="T5" t="n">
-        <v>-7.605399999999999</v>
+        <v>5.4051</v>
       </c>
       <c r="U5" t="n">
-        <v>-8.683300000000001</v>
+        <v>2.8683</v>
       </c>
       <c r="V5" t="n">
-        <v>19.9337</v>
+        <v>-10.4741</v>
       </c>
       <c r="W5" t="n">
-        <v>34.1042</v>
+        <v>6.5518</v>
       </c>
       <c r="X5" t="n">
-        <v>-14.1703</v>
+        <v>-17.0256</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>14</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2806</v>
+        <v>4.467599999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>3.5813</v>
+        <v>5.6022</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.3006</v>
+        <v>-1.1349</v>
       </c>
       <c r="G6" t="n">
         <v>22.1923</v>
@@ -922,13 +922,13 @@
         <v>26.1777</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.2545</v>
+        <v>1.932800000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7212</v>
+        <v>1.2995</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5328999999999999</v>
+        <v>0.6331999999999998</v>
       </c>
       <c r="V6" t="n">
         <v>0.1464999999999996</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. UDEZE</t>
+          <t>A. GANAL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.076300000000001</v>
+        <v>-3.3072</v>
       </c>
       <c r="E7" t="n">
-        <v>12.3593</v>
+        <v>-3.7474</v>
       </c>
       <c r="F7" t="n">
-        <v>-15.4355</v>
+        <v>0.4402</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.8314000000000004</v>
+        <v>-1.8551</v>
       </c>
       <c r="H7" t="n">
-        <v>0.08600000000000074</v>
+        <v>-0.5544</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.9177000000000002</v>
+        <v>-1.3007</v>
       </c>
       <c r="J7" t="n">
-        <v>16.3443</v>
+        <v>-2.158</v>
       </c>
       <c r="K7" t="n">
-        <v>11.727</v>
+        <v>-0.4966</v>
       </c>
       <c r="L7" t="n">
-        <v>4.6173</v>
+        <v>-1.6614</v>
       </c>
       <c r="M7" t="n">
-        <v>-17.1757</v>
+        <v>0.303</v>
       </c>
       <c r="N7" t="n">
-        <v>-11.6407</v>
+        <v>-0.0577</v>
       </c>
       <c r="O7" t="n">
-        <v>-5.534899999999999</v>
+        <v>0.3608</v>
       </c>
       <c r="P7" t="n">
-        <v>-5.690700000000001</v>
+        <v>-0.6830000000000001</v>
       </c>
       <c r="Q7" t="n">
-        <v>-24.3567</v>
+        <v>-1.1382</v>
       </c>
       <c r="R7" t="n">
-        <v>18.6661</v>
+        <v>0.4552</v>
       </c>
       <c r="S7" t="n">
-        <v>11.9895</v>
+        <v>0.004699999999999982</v>
       </c>
       <c r="T7" t="n">
-        <v>9.6614</v>
+        <v>0.3227</v>
       </c>
       <c r="U7" t="n">
-        <v>2.3279</v>
+        <v>-0.318</v>
       </c>
       <c r="V7" t="n">
-        <v>-8.542899999999999</v>
+        <v>-0.7739</v>
       </c>
       <c r="W7" t="n">
-        <v>10.7101</v>
+        <v>-0.7739</v>
       </c>
       <c r="X7" t="n">
-        <v>-19.2531</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. GANAL</t>
+          <t>S. OKOYE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,70 +1030,70 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.4468</v>
+        <v>-6.7752</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.6988</v>
+        <v>-1.304000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>0.252</v>
+        <v>-5.471299999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.8551</v>
+        <v>-12.5678</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5544</v>
+        <v>1.9874</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.3007</v>
+        <v>-14.5551</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.158</v>
+        <v>13.632</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.4966</v>
+        <v>19.8</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.6614</v>
+        <v>-6.1685</v>
       </c>
       <c r="M8" t="n">
-        <v>0.303</v>
+        <v>-26.1998</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0577</v>
+        <v>-17.8127</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3608</v>
+        <v>-8.387</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.6830000000000001</v>
+        <v>12.7473</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1382</v>
+        <v>-29.82</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4552</v>
+        <v>42.5674</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1348</v>
+        <v>-3.4423</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3714</v>
+        <v>-1.6309</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5062</v>
+        <v>-1.8113</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.7739</v>
+        <v>-3.5124</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.7739</v>
+        <v>16.5146</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-20.0275</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>-7.2754</v>
+        <v>-7.458699999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>-6.8094</v>
+        <v>-7.2135</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.466</v>
+        <v>-0.2452</v>
       </c>
       <c r="G9" t="n">
         <v>-1.0133</v>
@@ -1156,13 +1156,13 @@
         <v>3.4145</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3437</v>
+        <v>-0.5270999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4172</v>
+        <v>0.01319999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.7609</v>
+        <v>-0.5402</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. OKOYE</t>
+          <t>M. UDEZE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="D10" t="n">
-        <v>-10.5201</v>
+        <v>-11.1429</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.414899999999999</v>
+        <v>5.698499999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>-5.104799999999999</v>
+        <v>-16.8414</v>
       </c>
       <c r="G10" t="n">
-        <v>-12.5678</v>
+        <v>-0.8314000000000004</v>
       </c>
       <c r="H10" t="n">
-        <v>1.9874</v>
+        <v>0.08600000000000074</v>
       </c>
       <c r="I10" t="n">
-        <v>-14.5551</v>
+        <v>-0.9177000000000002</v>
       </c>
       <c r="J10" t="n">
-        <v>13.632</v>
+        <v>16.3443</v>
       </c>
       <c r="K10" t="n">
-        <v>19.8</v>
+        <v>11.727</v>
       </c>
       <c r="L10" t="n">
-        <v>-6.1685</v>
+        <v>4.6173</v>
       </c>
       <c r="M10" t="n">
-        <v>-26.1998</v>
+        <v>-17.1757</v>
       </c>
       <c r="N10" t="n">
-        <v>-17.8127</v>
+        <v>-11.6407</v>
       </c>
       <c r="O10" t="n">
-        <v>-8.387</v>
+        <v>-5.534899999999999</v>
       </c>
       <c r="P10" t="n">
-        <v>12.7473</v>
+        <v>-5.690700000000001</v>
       </c>
       <c r="Q10" t="n">
-        <v>-29.82</v>
+        <v>-24.3567</v>
       </c>
       <c r="R10" t="n">
-        <v>42.5674</v>
+        <v>18.6661</v>
       </c>
       <c r="S10" t="n">
-        <v>-7.187</v>
+        <v>3.9226</v>
       </c>
       <c r="T10" t="n">
-        <v>-5.7419</v>
+        <v>3.0005</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.445</v>
+        <v>0.9219000000000001</v>
       </c>
       <c r="V10" t="n">
-        <v>-3.5124</v>
+        <v>-8.542899999999999</v>
       </c>
       <c r="W10" t="n">
-        <v>16.5146</v>
+        <v>10.7101</v>
       </c>
       <c r="X10" t="n">
-        <v>-20.0275</v>
+        <v>-19.2531</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X. CASTANEDA</t>
+          <t>A. BEST</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="D11" t="n">
-        <v>-20.0646</v>
+        <v>-15.3444</v>
       </c>
       <c r="E11" t="n">
-        <v>-12.5966</v>
+        <v>-3.926299999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>-7.4678</v>
+        <v>-11.418</v>
       </c>
       <c r="G11" t="n">
-        <v>-14.022</v>
+        <v>-28.7917</v>
       </c>
       <c r="H11" t="n">
-        <v>-19.1958</v>
+        <v>-23.8937</v>
       </c>
       <c r="I11" t="n">
-        <v>5.1739</v>
+        <v>-4.8984</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.8908</v>
+        <v>5.4857</v>
       </c>
       <c r="K11" t="n">
-        <v>-9.1814</v>
+        <v>-6.434500000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>8.290699999999999</v>
+        <v>11.92</v>
       </c>
       <c r="M11" t="n">
-        <v>-13.1312</v>
+        <v>-34.2771</v>
       </c>
       <c r="N11" t="n">
-        <v>-10.0147</v>
+        <v>-17.4589</v>
       </c>
       <c r="O11" t="n">
-        <v>-3.1167</v>
+        <v>-16.8182</v>
       </c>
       <c r="P11" t="n">
-        <v>-7.284199999999999</v>
+        <v>11.837</v>
       </c>
       <c r="Q11" t="n">
-        <v>-17.5277</v>
+        <v>-40.7462</v>
       </c>
       <c r="R11" t="n">
-        <v>10.2436</v>
+        <v>52.5829</v>
       </c>
       <c r="S11" t="n">
-        <v>-4.5925</v>
+        <v>-9.7277</v>
       </c>
       <c r="T11" t="n">
-        <v>-5.4747</v>
+        <v>-2.225</v>
       </c>
       <c r="U11" t="n">
-        <v>0.8822</v>
+        <v>-7.502</v>
       </c>
       <c r="V11" t="n">
-        <v>5.8344</v>
+        <v>11.3382</v>
       </c>
       <c r="W11" t="n">
-        <v>11.2965</v>
+        <v>33.5595</v>
       </c>
       <c r="X11" t="n">
-        <v>-5.462499999999999</v>
+        <v>-22.2211</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>C. ORTEGA</t>
+          <t>X. CASTANEDA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="D12" t="n">
-        <v>-22.1566</v>
+        <v>-16.0034</v>
       </c>
       <c r="E12" t="n">
-        <v>-16.8958</v>
+        <v>-9.1965</v>
       </c>
       <c r="F12" t="n">
-        <v>-5.2607</v>
+        <v>-6.806999999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>-24.3234</v>
+        <v>-14.022</v>
       </c>
       <c r="H12" t="n">
-        <v>-19.8714</v>
+        <v>-19.1958</v>
       </c>
       <c r="I12" t="n">
-        <v>-4.4522</v>
+        <v>5.1739</v>
       </c>
       <c r="J12" t="n">
-        <v>-8.135</v>
+        <v>-0.8908</v>
       </c>
       <c r="K12" t="n">
-        <v>-5.3959</v>
+        <v>-9.1814</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.7392</v>
+        <v>8.290699999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>-16.1886</v>
+        <v>-13.1312</v>
       </c>
       <c r="N12" t="n">
-        <v>-14.4755</v>
+        <v>-10.0147</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.713</v>
+        <v>-3.1167</v>
       </c>
       <c r="P12" t="n">
-        <v>11.1541</v>
+        <v>-7.284199999999999</v>
       </c>
       <c r="Q12" t="n">
-        <v>-14.1133</v>
+        <v>-17.5277</v>
       </c>
       <c r="R12" t="n">
-        <v>25.2673</v>
+        <v>10.2436</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.7279</v>
+        <v>-0.5313</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.905</v>
+        <v>-2.0745</v>
       </c>
       <c r="U12" t="n">
-        <v>0.177</v>
+        <v>1.5431</v>
       </c>
       <c r="V12" t="n">
-        <v>-6.258600000000001</v>
+        <v>5.8344</v>
       </c>
       <c r="W12" t="n">
-        <v>8.2577</v>
+        <v>11.2965</v>
       </c>
       <c r="X12" t="n">
-        <v>-14.5163</v>
+        <v>-5.462499999999999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>K. KOSTADINOV</t>
+          <t>C. ORTEGA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="D13" t="n">
-        <v>-22.6408</v>
+        <v>-19.4888</v>
       </c>
       <c r="E13" t="n">
-        <v>3.437100000000001</v>
+        <v>-14.4565</v>
       </c>
       <c r="F13" t="n">
-        <v>-26.0779</v>
+        <v>-5.0324</v>
       </c>
       <c r="G13" t="n">
-        <v>-7.879099999999999</v>
+        <v>-24.3234</v>
       </c>
       <c r="H13" t="n">
-        <v>-6.1991</v>
+        <v>-19.8714</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.6804</v>
+        <v>-4.4522</v>
       </c>
       <c r="J13" t="n">
-        <v>12.963</v>
+        <v>-8.135</v>
       </c>
       <c r="K13" t="n">
-        <v>8.7342</v>
+        <v>-5.3959</v>
       </c>
       <c r="L13" t="n">
-        <v>4.2287</v>
+        <v>-2.7392</v>
       </c>
       <c r="M13" t="n">
-        <v>-20.842</v>
+        <v>-16.1886</v>
       </c>
       <c r="N13" t="n">
-        <v>-14.9331</v>
+        <v>-14.4755</v>
       </c>
       <c r="O13" t="n">
-        <v>-5.9091</v>
+        <v>-1.713</v>
       </c>
       <c r="P13" t="n">
-        <v>-4.5527</v>
+        <v>11.1541</v>
       </c>
       <c r="Q13" t="n">
-        <v>-27.9988</v>
+        <v>-14.1133</v>
       </c>
       <c r="R13" t="n">
-        <v>23.4464</v>
+        <v>25.2673</v>
       </c>
       <c r="S13" t="n">
-        <v>8.5185</v>
+        <v>-0.06069999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>12.3085</v>
+        <v>-0.4659</v>
       </c>
       <c r="U13" t="n">
-        <v>-3.7892</v>
+        <v>0.4055</v>
       </c>
       <c r="V13" t="n">
-        <v>-18.7276</v>
+        <v>-6.258600000000001</v>
       </c>
       <c r="W13" t="n">
-        <v>6.1646</v>
+        <v>8.2577</v>
       </c>
       <c r="X13" t="n">
-        <v>-24.8923</v>
+        <v>-14.5163</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. BEST</t>
+          <t>Y. PONS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D14" t="n">
-        <v>-27.5442</v>
+        <v>-20.8028</v>
       </c>
       <c r="E14" t="n">
-        <v>-9.019899999999998</v>
+        <v>-3.0419</v>
       </c>
       <c r="F14" t="n">
-        <v>-18.5241</v>
+        <v>-17.7613</v>
       </c>
       <c r="G14" t="n">
-        <v>-28.7917</v>
+        <v>-5.2949</v>
       </c>
       <c r="H14" t="n">
-        <v>-23.8937</v>
+        <v>-3.676399999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>-4.8984</v>
+        <v>-1.6185</v>
       </c>
       <c r="J14" t="n">
-        <v>5.4857</v>
+        <v>20.0337</v>
       </c>
       <c r="K14" t="n">
-        <v>-6.434500000000001</v>
+        <v>11.2107</v>
       </c>
       <c r="L14" t="n">
-        <v>11.92</v>
+        <v>8.822700000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>-34.2771</v>
+        <v>-25.3285</v>
       </c>
       <c r="N14" t="n">
-        <v>-17.4589</v>
+        <v>-14.8872</v>
       </c>
       <c r="O14" t="n">
-        <v>-16.8182</v>
+        <v>-10.4419</v>
       </c>
       <c r="P14" t="n">
-        <v>11.837</v>
+        <v>20.487</v>
       </c>
       <c r="Q14" t="n">
-        <v>-40.7462</v>
+        <v>-25.2674</v>
       </c>
       <c r="R14" t="n">
-        <v>52.5829</v>
+        <v>45.7543</v>
       </c>
       <c r="S14" t="n">
-        <v>-21.9275</v>
+        <v>-8.112</v>
       </c>
       <c r="T14" t="n">
-        <v>-7.3188</v>
+        <v>-3.8153</v>
       </c>
       <c r="U14" t="n">
-        <v>-14.6085</v>
+        <v>-4.2971</v>
       </c>
       <c r="V14" t="n">
-        <v>11.3382</v>
+        <v>-27.8829</v>
       </c>
       <c r="W14" t="n">
-        <v>33.5595</v>
+        <v>6.0073</v>
       </c>
       <c r="X14" t="n">
-        <v>-22.2211</v>
+        <v>-33.89</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Y. PONS</t>
+          <t>K. KOSTADINOV</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,70 +1576,70 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="D15" t="n">
-        <v>-29.0368</v>
+        <v>-30.0379</v>
       </c>
       <c r="E15" t="n">
-        <v>-9.1594</v>
+        <v>-4.624000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>-19.8773</v>
+        <v>-25.414</v>
       </c>
       <c r="G15" t="n">
-        <v>-5.2949</v>
+        <v>-7.879099999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>-3.676399999999999</v>
+        <v>-6.1991</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.6185</v>
+        <v>-1.6804</v>
       </c>
       <c r="J15" t="n">
-        <v>20.0337</v>
+        <v>12.963</v>
       </c>
       <c r="K15" t="n">
-        <v>11.2107</v>
+        <v>8.7342</v>
       </c>
       <c r="L15" t="n">
-        <v>8.822700000000001</v>
+        <v>4.2287</v>
       </c>
       <c r="M15" t="n">
-        <v>-25.3285</v>
+        <v>-20.842</v>
       </c>
       <c r="N15" t="n">
-        <v>-14.8872</v>
+        <v>-14.9331</v>
       </c>
       <c r="O15" t="n">
-        <v>-10.4419</v>
+        <v>-5.9091</v>
       </c>
       <c r="P15" t="n">
-        <v>20.487</v>
+        <v>-4.5527</v>
       </c>
       <c r="Q15" t="n">
-        <v>-25.2674</v>
+        <v>-27.9988</v>
       </c>
       <c r="R15" t="n">
-        <v>45.7543</v>
+        <v>23.4464</v>
       </c>
       <c r="S15" t="n">
-        <v>-16.3457</v>
+        <v>1.1214</v>
       </c>
       <c r="T15" t="n">
-        <v>-9.933</v>
+        <v>4.247</v>
       </c>
       <c r="U15" t="n">
-        <v>-6.413</v>
+        <v>-3.1252</v>
       </c>
       <c r="V15" t="n">
-        <v>-27.8829</v>
+        <v>-18.7276</v>
       </c>
       <c r="W15" t="n">
-        <v>6.0073</v>
+        <v>6.1646</v>
       </c>
       <c r="X15" t="n">
-        <v>-33.89</v>
+        <v>-24.8923</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>32</v>
       </c>
       <c r="D16" t="n">
-        <v>-34.8152</v>
+        <v>-34.2179</v>
       </c>
       <c r="E16" t="n">
-        <v>-19.8745</v>
+        <v>-19.5045</v>
       </c>
       <c r="F16" t="n">
-        <v>-14.9407</v>
+        <v>-14.7136</v>
       </c>
       <c r="G16" t="n">
         <v>-53.0745</v>
@@ -1702,13 +1702,13 @@
         <v>38.6974</v>
       </c>
       <c r="S16" t="n">
-        <v>6.8795</v>
+        <v>7.4769</v>
       </c>
       <c r="T16" t="n">
-        <v>5.6941</v>
+        <v>6.0644</v>
       </c>
       <c r="U16" t="n">
-        <v>1.1856</v>
+        <v>1.4123</v>
       </c>
       <c r="V16" t="n">
         <v>1.3639</v>
@@ -1735,13 +1735,13 @@
         <v>32</v>
       </c>
       <c r="D17" t="n">
-        <v>-72.46470000000001</v>
+        <v>-48.8128</v>
       </c>
       <c r="E17" t="n">
-        <v>-42.9263</v>
+        <v>-24.8734</v>
       </c>
       <c r="F17" t="n">
-        <v>-29.5382</v>
+        <v>-23.9393</v>
       </c>
       <c r="G17" t="n">
         <v>-4.2683</v>
@@ -1780,13 +1780,13 @@
         <v>57.5909</v>
       </c>
       <c r="S17" t="n">
-        <v>-34.3936</v>
+        <v>-10.742</v>
       </c>
       <c r="T17" t="n">
-        <v>-20.3264</v>
+        <v>-2.2734</v>
       </c>
       <c r="U17" t="n">
-        <v>-14.0671</v>
+        <v>-8.4687</v>
       </c>
       <c r="V17" t="n">
         <v>26.0645</v>
@@ -1813,13 +1813,13 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>-159.9624</v>
+        <v>-128.4633</v>
       </c>
       <c r="E18" t="n">
-        <v>20.2052</v>
+        <v>32.75039999999998</v>
       </c>
       <c r="F18" t="n">
-        <v>-180.1656</v>
+        <v>-161.2148</v>
       </c>
       <c r="G18" t="n">
         <v>-63.27160000000001</v>
@@ -1852,22 +1852,22 @@
         <v>-77.3938</v>
       </c>
       <c r="Q18" t="n">
-        <v>-553.1469999999999</v>
+        <v>-553.147</v>
       </c>
       <c r="R18" t="n">
         <v>475.7523</v>
       </c>
       <c r="S18" t="n">
-        <v>-36.7644</v>
+        <v>-5.266200000000003</v>
       </c>
       <c r="T18" t="n">
-        <v>4.458300000000001</v>
+        <v>17.005</v>
       </c>
       <c r="U18" t="n">
-        <v>-41.2214</v>
+        <v>-22.2702</v>
       </c>
       <c r="V18" t="n">
-        <v>17.47030000000001</v>
+        <v>17.47030000000002</v>
       </c>
       <c r="W18" t="n">
         <v>287.7347</v>
